--- a/docs/詳細設計書/詳細設計書_在庫一覧画面_API編.xlsx
+++ b/docs/詳細設計書/詳細設計書_在庫一覧画面_API編.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\詳細設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB01CB0-91FE-4E71-8AE1-4CF6371EFA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122E965A-D7A4-4F52-9AAB-3420D8522FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{94E1F5D5-5A75-8F40-A2A1-CC833EFCF558}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{94E1F5D5-5A75-8F40-A2A1-CC833EFCF558}"/>
   </bookViews>
   <sheets>
     <sheet name="機能概要" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="テーブル編集仕様" sheetId="9" state="hidden" r:id="rId8"/>
     <sheet name="補足説明" sheetId="10" state="hidden" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">画面イメージ＿検索機能!$A$1:$AO$209</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="172">
   <si>
     <t>システム名</t>
     <phoneticPr fontId="1"/>
@@ -1410,12 +1413,149 @@
     <t xml:space="preserve">GET http://localhost:8080/stock-info/name/{name}/amount/{amount}/than/{than} </t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>操作内容はログとして出力する。（ログ出力の詳細は共通資料参照）</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.ログ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.2入力チェック</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力項目「個数」に以下のような入力値がある場合、再検索を促すエラーメッセージを表示する。</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクコウモク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ニュウリョクチ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ウナガ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力値</t>
+    <rPh sb="0" eb="1">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラーメッセージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0未満</t>
+    <rPh sb="1" eb="3">
+      <t>ミマン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>個数は正の整数でなければなりません</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※個数は正の整数でなければなりません</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索項目「個数」にマイナス値が入力された状態で「検索」ボタンが押下された場合、エラーメッセージを出力される。</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1510,6 +1650,12 @@
       <u/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1725,7 +1871,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2100,6 +2246,39 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7439,7 +7618,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A1A97F-56E4-6648-9A48-958A7171C634}">
-  <dimension ref="A1:AO43"/>
+  <dimension ref="A1:AO51"/>
   <sheetFormatPr defaultColWidth="3.77734375" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="3.77734375" style="2"/>
@@ -9144,9 +9323,6 @@
       <c r="G38" s="30"/>
       <c r="H38" s="17"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -9186,28 +9362,11 @@
       <c r="F39" s="30"/>
       <c r="G39" s="30"/>
       <c r="H39" s="17"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="30"/>
-      <c r="AD39" s="30"/>
       <c r="AE39" s="18"/>
       <c r="AF39" s="30"/>
       <c r="AG39" s="30"/>
@@ -9242,70 +9401,404 @@
       <c r="AO40" s="18"/>
     </row>
     <row r="41" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="86"/>
-      <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
       <c r="H41" s="17"/>
+      <c r="K41" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="1"/>
       <c r="AE41" s="18"/>
-      <c r="AF41" s="84"/>
-      <c r="AG41" s="84"/>
-      <c r="AH41" s="84"/>
-      <c r="AI41" s="84"/>
-      <c r="AJ41" s="84"/>
-      <c r="AK41" s="84"/>
-      <c r="AL41" s="85"/>
+      <c r="AF41" s="30"/>
+      <c r="AG41" s="30"/>
+      <c r="AH41" s="30"/>
+      <c r="AI41" s="30"/>
+      <c r="AJ41" s="30"/>
+      <c r="AK41" s="30"/>
+      <c r="AL41" s="31"/>
       <c r="AM41" s="1"/>
       <c r="AN41" s="1"/>
       <c r="AO41" s="18"/>
     </row>
     <row r="42" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="86"/>
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
       <c r="H42" s="17"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="125" t="s">
+        <v>165</v>
+      </c>
+      <c r="L42" s="125"/>
+      <c r="M42" s="125"/>
+      <c r="N42" s="125"/>
+      <c r="O42" s="125"/>
+      <c r="P42" s="126" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q42" s="127"/>
+      <c r="R42" s="127"/>
+      <c r="S42" s="127"/>
+      <c r="T42" s="127"/>
+      <c r="U42" s="127"/>
+      <c r="V42" s="127"/>
+      <c r="W42" s="127"/>
+      <c r="X42" s="127"/>
+      <c r="Y42" s="127"/>
+      <c r="Z42" s="128"/>
+      <c r="AA42" s="54" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB42" s="54"/>
+      <c r="AC42" s="54"/>
+      <c r="AD42" s="54"/>
       <c r="AE42" s="18"/>
-      <c r="AF42" s="84"/>
-      <c r="AG42" s="84"/>
-      <c r="AH42" s="84"/>
-      <c r="AI42" s="84"/>
-      <c r="AJ42" s="84"/>
-      <c r="AK42" s="84"/>
-      <c r="AL42" s="85"/>
+      <c r="AF42" s="30"/>
+      <c r="AG42" s="30"/>
+      <c r="AH42" s="30"/>
+      <c r="AI42" s="30"/>
+      <c r="AJ42" s="30"/>
+      <c r="AK42" s="30"/>
+      <c r="AL42" s="31"/>
       <c r="AM42" s="1"/>
       <c r="AN42" s="1"/>
       <c r="AO42" s="18"/>
     </row>
     <row r="43" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="79"/>
-      <c r="B43" s="80"/>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
-      <c r="E43" s="80"/>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="20"/>
-      <c r="AE43" s="22"/>
-      <c r="AF43" s="80"/>
-      <c r="AG43" s="80"/>
-      <c r="AH43" s="80"/>
-      <c r="AI43" s="80"/>
-      <c r="AJ43" s="80"/>
-      <c r="AK43" s="80"/>
-      <c r="AL43" s="81"/>
-      <c r="AM43" s="21"/>
-      <c r="AN43" s="21"/>
-      <c r="AO43" s="22"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="110" t="s">
+        <v>168</v>
+      </c>
+      <c r="L43" s="110"/>
+      <c r="M43" s="110"/>
+      <c r="N43" s="110"/>
+      <c r="O43" s="110"/>
+      <c r="P43" s="132" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q43" s="133"/>
+      <c r="R43" s="133"/>
+      <c r="S43" s="133"/>
+      <c r="T43" s="133"/>
+      <c r="U43" s="133"/>
+      <c r="V43" s="133"/>
+      <c r="W43" s="133"/>
+      <c r="X43" s="133"/>
+      <c r="Y43" s="133"/>
+      <c r="Z43" s="134"/>
+      <c r="AA43" s="129"/>
+      <c r="AB43" s="130"/>
+      <c r="AC43" s="130"/>
+      <c r="AD43" s="131"/>
+      <c r="AE43" s="18"/>
+      <c r="AF43" s="30"/>
+      <c r="AG43" s="30"/>
+      <c r="AH43" s="30"/>
+      <c r="AI43" s="30"/>
+      <c r="AJ43" s="30"/>
+      <c r="AK43" s="30"/>
+      <c r="AL43" s="31"/>
+      <c r="AM43" s="1"/>
+      <c r="AN43" s="1"/>
+      <c r="AO43" s="18"/>
+    </row>
+    <row r="44" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="29"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="AE44" s="18"/>
+      <c r="AF44" s="30"/>
+      <c r="AG44" s="30"/>
+      <c r="AH44" s="30"/>
+      <c r="AI44" s="30"/>
+      <c r="AJ44" s="30"/>
+      <c r="AK44" s="30"/>
+      <c r="AL44" s="31"/>
+      <c r="AM44" s="1"/>
+      <c r="AN44" s="1"/>
+      <c r="AO44" s="18"/>
+    </row>
+    <row r="45" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="29"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="30"/>
+      <c r="AD45" s="30"/>
+      <c r="AE45" s="18"/>
+      <c r="AF45" s="30"/>
+      <c r="AG45" s="30"/>
+      <c r="AH45" s="30"/>
+      <c r="AI45" s="30"/>
+      <c r="AJ45" s="30"/>
+      <c r="AK45" s="30"/>
+      <c r="AL45" s="31"/>
+      <c r="AM45" s="1"/>
+      <c r="AN45" s="1"/>
+      <c r="AO45" s="18"/>
+    </row>
+    <row r="46" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="29"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+      <c r="AE46" s="18"/>
+      <c r="AF46" s="30"/>
+      <c r="AG46" s="30"/>
+      <c r="AH46" s="30"/>
+      <c r="AI46" s="30"/>
+      <c r="AJ46" s="30"/>
+      <c r="AK46" s="30"/>
+      <c r="AL46" s="31"/>
+      <c r="AM46" s="1"/>
+      <c r="AN46" s="1"/>
+      <c r="AO46" s="18"/>
+    </row>
+    <row r="47" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="29"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+      <c r="AE47" s="18"/>
+      <c r="AF47" s="30"/>
+      <c r="AG47" s="30"/>
+      <c r="AH47" s="30"/>
+      <c r="AI47" s="30"/>
+      <c r="AJ47" s="30"/>
+      <c r="AK47" s="30"/>
+      <c r="AL47" s="31"/>
+      <c r="AM47" s="1"/>
+      <c r="AN47" s="1"/>
+      <c r="AO47" s="18"/>
+    </row>
+    <row r="48" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="29"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+      <c r="AE48" s="18"/>
+      <c r="AF48" s="30"/>
+      <c r="AG48" s="30"/>
+      <c r="AH48" s="30"/>
+      <c r="AI48" s="30"/>
+      <c r="AJ48" s="30"/>
+      <c r="AK48" s="30"/>
+      <c r="AL48" s="31"/>
+      <c r="AM48" s="1"/>
+      <c r="AN48" s="1"/>
+      <c r="AO48" s="18"/>
+    </row>
+    <row r="49" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="86"/>
+      <c r="B49" s="84"/>
+      <c r="C49" s="84"/>
+      <c r="D49" s="84"/>
+      <c r="E49" s="84"/>
+      <c r="F49" s="84"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="17"/>
+      <c r="AE49" s="18"/>
+      <c r="AF49" s="84"/>
+      <c r="AG49" s="84"/>
+      <c r="AH49" s="84"/>
+      <c r="AI49" s="84"/>
+      <c r="AJ49" s="84"/>
+      <c r="AK49" s="84"/>
+      <c r="AL49" s="85"/>
+      <c r="AM49" s="1"/>
+      <c r="AN49" s="1"/>
+      <c r="AO49" s="18"/>
+    </row>
+    <row r="50" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="86"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="17"/>
+      <c r="AE50" s="18"/>
+      <c r="AF50" s="84"/>
+      <c r="AG50" s="84"/>
+      <c r="AH50" s="84"/>
+      <c r="AI50" s="84"/>
+      <c r="AJ50" s="84"/>
+      <c r="AK50" s="84"/>
+      <c r="AL50" s="85"/>
+      <c r="AM50" s="1"/>
+      <c r="AN50" s="1"/>
+      <c r="AO50" s="18"/>
+    </row>
+    <row r="51" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="79"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="80"/>
+      <c r="D51" s="80"/>
+      <c r="E51" s="80"/>
+      <c r="F51" s="80"/>
+      <c r="G51" s="80"/>
+      <c r="H51" s="20"/>
+      <c r="AE51" s="22"/>
+      <c r="AF51" s="80"/>
+      <c r="AG51" s="80"/>
+      <c r="AH51" s="80"/>
+      <c r="AI51" s="80"/>
+      <c r="AJ51" s="80"/>
+      <c r="AK51" s="80"/>
+      <c r="AL51" s="81"/>
+      <c r="AM51" s="21"/>
+      <c r="AN51" s="21"/>
+      <c r="AO51" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="55">
+    <mergeCell ref="AA42:AD42"/>
+    <mergeCell ref="K43:O43"/>
+    <mergeCell ref="P43:Z43"/>
+    <mergeCell ref="AA43:AD43"/>
     <mergeCell ref="AL1:AO2"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="T2:AA2"/>
@@ -9341,20 +9834,22 @@
     <mergeCell ref="AF8:AL8"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="AF9:AL9"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="AF43:AL43"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="AF51:AL51"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="AF14:AL14"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="AF15:AL15"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="AF16:AL16"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="AF42:AL42"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="AF50:AL50"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="AF40:AL40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="AF41:AL41"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="AF49:AL49"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="P42:Z42"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10722,7 +11217,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B21B65-96F3-46AA-AC96-08DB070B9BAA}">
-  <dimension ref="A1:AO189"/>
+  <dimension ref="A1:AO194"/>
   <sheetFormatPr defaultColWidth="3.77734375" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="3.77734375" style="2"/>
@@ -15878,7 +16373,7 @@
       <c r="AM160" s="7"/>
       <c r="AO160" s="8"/>
     </row>
-    <row r="161" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C161" s="7"/>
       <c r="G161" s="8"/>
       <c r="J161" s="73"/>
@@ -15909,7 +16404,7 @@
       <c r="AM161" s="7"/>
       <c r="AO161" s="8"/>
     </row>
-    <row r="162" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C162" s="7"/>
       <c r="G162" s="8"/>
       <c r="J162" s="73"/>
@@ -15940,7 +16435,7 @@
       <c r="AM162" s="7"/>
       <c r="AO162" s="8"/>
     </row>
-    <row r="163" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C163" s="7"/>
       <c r="G163" s="8"/>
       <c r="J163" s="73"/>
@@ -15971,7 +16466,7 @@
       <c r="AM163" s="7"/>
       <c r="AO163" s="8"/>
     </row>
-    <row r="164" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C164" s="7"/>
       <c r="G164" s="8"/>
       <c r="J164" s="73"/>
@@ -16002,7 +16497,7 @@
       <c r="AM164" s="7"/>
       <c r="AO164" s="8"/>
     </row>
-    <row r="165" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C165" s="7"/>
       <c r="G165" s="8"/>
       <c r="J165" s="73"/>
@@ -16033,14 +16528,14 @@
       <c r="AM165" s="7"/>
       <c r="AO165" s="8"/>
     </row>
-    <row r="166" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C166" s="7"/>
       <c r="G166" s="8"/>
       <c r="AJ166" s="8"/>
       <c r="AM166" s="7"/>
       <c r="AO166" s="8"/>
     </row>
-    <row r="167" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C167" s="9"/>
       <c r="D167" s="10"/>
       <c r="E167" s="10"/>
@@ -16078,87 +16573,820 @@
       <c r="AM167" s="7"/>
       <c r="AO167" s="8"/>
     </row>
-    <row r="168" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C168" s="135"/>
+      <c r="D168" s="135"/>
+      <c r="E168" s="135"/>
+      <c r="F168" s="135"/>
+      <c r="G168" s="135"/>
+      <c r="H168" s="135"/>
+      <c r="I168" s="135"/>
+      <c r="J168" s="135"/>
+      <c r="K168" s="135"/>
+      <c r="L168" s="135"/>
+      <c r="M168" s="135"/>
+      <c r="N168" s="135"/>
+      <c r="O168" s="135"/>
+      <c r="P168" s="135"/>
+      <c r="Q168" s="135"/>
+      <c r="R168" s="135"/>
+      <c r="S168" s="135"/>
+      <c r="T168" s="135"/>
+      <c r="U168" s="135"/>
+      <c r="V168" s="135"/>
+      <c r="W168" s="135"/>
+      <c r="X168" s="135"/>
+      <c r="Y168" s="135"/>
+      <c r="Z168" s="135"/>
+      <c r="AA168" s="135"/>
+      <c r="AB168" s="135"/>
+      <c r="AC168" s="135"/>
+      <c r="AD168" s="135"/>
+      <c r="AE168" s="135"/>
+      <c r="AF168" s="135"/>
+      <c r="AG168" s="135"/>
+      <c r="AH168" s="135"/>
+      <c r="AI168" s="135"/>
+      <c r="AJ168" s="135"/>
       <c r="AM168" s="7"/>
       <c r="AO168" s="8"/>
     </row>
-    <row r="169" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="AM169" s="7"/>
       <c r="AO169" s="8"/>
     </row>
-    <row r="170" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B170" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="AM170" s="7"/>
       <c r="AO170" s="8"/>
     </row>
-    <row r="171" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C171" s="4"/>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5"/>
+      <c r="G171" s="6"/>
+      <c r="H171" s="4"/>
+      <c r="I171" s="5"/>
+      <c r="J171" s="5"/>
+      <c r="K171" s="5"/>
+      <c r="L171" s="5"/>
+      <c r="M171" s="5"/>
+      <c r="N171" s="5"/>
+      <c r="O171" s="5"/>
+      <c r="P171" s="5"/>
+      <c r="Q171" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="R171" s="5"/>
+      <c r="S171" s="5"/>
+      <c r="T171" s="5"/>
+      <c r="U171" s="5"/>
+      <c r="V171" s="5"/>
+      <c r="W171" s="5"/>
+      <c r="X171" s="5"/>
+      <c r="Y171" s="5"/>
+      <c r="Z171" s="5"/>
+      <c r="AA171" s="5"/>
+      <c r="AB171" s="5"/>
+      <c r="AC171" s="5"/>
+      <c r="AD171" s="5"/>
+      <c r="AE171" s="5"/>
+      <c r="AF171" s="5"/>
+      <c r="AG171" s="5"/>
+      <c r="AH171" s="5"/>
+      <c r="AI171" s="5"/>
+      <c r="AJ171" s="6"/>
       <c r="AM171" s="7"/>
       <c r="AO171" s="8"/>
     </row>
-    <row r="172" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C172" s="7"/>
+      <c r="D172" s="95"/>
+      <c r="E172" s="95"/>
+      <c r="F172" s="95"/>
+      <c r="G172" s="8"/>
+      <c r="H172" s="9"/>
+      <c r="I172" s="10"/>
+      <c r="J172" s="10"/>
+      <c r="K172" s="10"/>
+      <c r="L172" s="10"/>
+      <c r="M172" s="10"/>
+      <c r="N172" s="10"/>
+      <c r="O172" s="10"/>
+      <c r="P172" s="10"/>
+      <c r="Q172" s="10"/>
+      <c r="R172" s="10"/>
+      <c r="S172" s="10"/>
+      <c r="T172" s="10"/>
+      <c r="U172" s="10"/>
+      <c r="V172" s="10"/>
+      <c r="W172" s="10"/>
+      <c r="X172" s="10"/>
+      <c r="Y172" s="10"/>
+      <c r="Z172" s="10"/>
+      <c r="AA172" s="10"/>
+      <c r="AB172" s="10"/>
+      <c r="AC172" s="10"/>
+      <c r="AD172" s="10"/>
+      <c r="AE172" s="10"/>
+      <c r="AF172" s="10"/>
+      <c r="AG172" s="10"/>
+      <c r="AH172" s="10"/>
+      <c r="AI172" s="10"/>
+      <c r="AJ172" s="11"/>
       <c r="AM172" s="7"/>
       <c r="AO172" s="8"/>
     </row>
-    <row r="173" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C173" s="7"/>
+      <c r="G173" s="8"/>
+      <c r="AJ173" s="8"/>
       <c r="AM173" s="7"/>
       <c r="AO173" s="8"/>
     </row>
-    <row r="174" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C174" s="7"/>
+      <c r="G174" s="8"/>
+      <c r="H174" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ174" s="8"/>
       <c r="AM174" s="7"/>
       <c r="AO174" s="8"/>
     </row>
-    <row r="175" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C175" s="7"/>
+      <c r="G175" s="8"/>
+      <c r="J175" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="M175" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N175" s="92"/>
+      <c r="O175" s="93"/>
+      <c r="P175" s="93"/>
+      <c r="Q175" s="94"/>
+      <c r="S175" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T175" s="92"/>
+      <c r="U175" s="93"/>
+      <c r="V175" s="93"/>
+      <c r="W175" s="94"/>
+      <c r="Y175" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z175" s="92">
+        <v>1</v>
+      </c>
+      <c r="AA175" s="94"/>
+      <c r="AB175" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC175" s="73"/>
+      <c r="AF175" s="104" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG175" s="104"/>
+      <c r="AJ175" s="8"/>
       <c r="AM175" s="7"/>
       <c r="AO175" s="8"/>
     </row>
-    <row r="176" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="2:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C176" s="7"/>
+      <c r="G176" s="8"/>
+      <c r="Q176" s="32"/>
+      <c r="R176" s="32"/>
+      <c r="AJ176" s="8"/>
       <c r="AM176" s="7"/>
       <c r="AO176" s="8"/>
     </row>
-    <row r="177" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C177" s="7"/>
+      <c r="G177" s="8"/>
+      <c r="J177" s="96" t="s">
+        <v>58</v>
+      </c>
+      <c r="K177" s="96"/>
+      <c r="L177" s="96"/>
+      <c r="M177" s="96"/>
+      <c r="N177" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="O177" s="96"/>
+      <c r="P177" s="96"/>
+      <c r="Q177" s="96"/>
+      <c r="R177" s="96" t="s">
+        <v>39</v>
+      </c>
+      <c r="S177" s="96"/>
+      <c r="T177" s="97" t="s">
+        <v>92</v>
+      </c>
+      <c r="U177" s="97"/>
+      <c r="V177" s="97"/>
+      <c r="W177" s="97"/>
+      <c r="X177" s="97"/>
+      <c r="Y177" s="98" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z177" s="99"/>
+      <c r="AA177" s="99"/>
+      <c r="AB177" s="99"/>
+      <c r="AC177" s="99"/>
+      <c r="AD177" s="99"/>
+      <c r="AE177" s="99"/>
+      <c r="AF177" s="99"/>
+      <c r="AG177" s="100"/>
+      <c r="AJ177" s="8"/>
       <c r="AM177" s="7"/>
       <c r="AO177" s="8"/>
     </row>
-    <row r="178" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C178" s="7"/>
+      <c r="G178" s="8"/>
+      <c r="J178" s="73"/>
+      <c r="K178" s="73"/>
+      <c r="L178" s="73"/>
+      <c r="M178" s="73"/>
+      <c r="N178" s="73"/>
+      <c r="O178" s="73"/>
+      <c r="P178" s="73"/>
+      <c r="Q178" s="73"/>
+      <c r="R178" s="73"/>
+      <c r="S178" s="73"/>
+      <c r="T178" s="73"/>
+      <c r="U178" s="73"/>
+      <c r="V178" s="73"/>
+      <c r="W178" s="73"/>
+      <c r="X178" s="73"/>
+      <c r="Y178" s="92"/>
+      <c r="Z178" s="93"/>
+      <c r="AA178" s="93"/>
+      <c r="AB178" s="93"/>
+      <c r="AC178" s="93"/>
+      <c r="AD178" s="93"/>
+      <c r="AE178" s="93"/>
+      <c r="AF178" s="93"/>
+      <c r="AG178" s="94"/>
+      <c r="AJ178" s="8"/>
       <c r="AM178" s="7"/>
       <c r="AO178" s="8"/>
     </row>
-    <row r="179" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C179" s="7"/>
+      <c r="G179" s="8"/>
+      <c r="J179" s="73"/>
+      <c r="K179" s="73"/>
+      <c r="L179" s="73"/>
+      <c r="M179" s="73"/>
+      <c r="N179" s="73"/>
+      <c r="O179" s="73"/>
+      <c r="P179" s="73"/>
+      <c r="Q179" s="73"/>
+      <c r="R179" s="73"/>
+      <c r="S179" s="73"/>
+      <c r="T179" s="92"/>
+      <c r="U179" s="93"/>
+      <c r="V179" s="93"/>
+      <c r="W179" s="93"/>
+      <c r="X179" s="94"/>
+      <c r="Y179" s="92"/>
+      <c r="Z179" s="93"/>
+      <c r="AA179" s="93"/>
+      <c r="AB179" s="93"/>
+      <c r="AC179" s="93"/>
+      <c r="AD179" s="93"/>
+      <c r="AE179" s="93"/>
+      <c r="AF179" s="93"/>
+      <c r="AG179" s="94"/>
+      <c r="AJ179" s="8"/>
       <c r="AM179" s="7"/>
       <c r="AO179" s="8"/>
     </row>
-    <row r="180" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C180" s="7"/>
+      <c r="G180" s="8"/>
+      <c r="J180" s="73"/>
+      <c r="K180" s="73"/>
+      <c r="L180" s="73"/>
+      <c r="M180" s="73"/>
+      <c r="N180" s="73"/>
+      <c r="O180" s="73"/>
+      <c r="P180" s="73"/>
+      <c r="Q180" s="73"/>
+      <c r="R180" s="73"/>
+      <c r="S180" s="73"/>
+      <c r="T180" s="92"/>
+      <c r="U180" s="93"/>
+      <c r="V180" s="93"/>
+      <c r="W180" s="93"/>
+      <c r="X180" s="94"/>
+      <c r="Y180" s="92"/>
+      <c r="Z180" s="93"/>
+      <c r="AA180" s="93"/>
+      <c r="AB180" s="93"/>
+      <c r="AC180" s="93"/>
+      <c r="AD180" s="93"/>
+      <c r="AE180" s="93"/>
+      <c r="AF180" s="93"/>
+      <c r="AG180" s="94"/>
+      <c r="AJ180" s="8"/>
       <c r="AM180" s="7"/>
       <c r="AO180" s="8"/>
     </row>
-    <row r="181" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C181" s="7"/>
+      <c r="G181" s="8"/>
+      <c r="J181" s="73"/>
+      <c r="K181" s="73"/>
+      <c r="L181" s="73"/>
+      <c r="M181" s="73"/>
+      <c r="N181" s="73"/>
+      <c r="O181" s="73"/>
+      <c r="P181" s="73"/>
+      <c r="Q181" s="73"/>
+      <c r="R181" s="73"/>
+      <c r="S181" s="73"/>
+      <c r="T181" s="92"/>
+      <c r="U181" s="93"/>
+      <c r="V181" s="93"/>
+      <c r="W181" s="93"/>
+      <c r="X181" s="94"/>
+      <c r="Y181" s="92"/>
+      <c r="Z181" s="93"/>
+      <c r="AA181" s="93"/>
+      <c r="AB181" s="93"/>
+      <c r="AC181" s="93"/>
+      <c r="AD181" s="93"/>
+      <c r="AE181" s="93"/>
+      <c r="AF181" s="93"/>
+      <c r="AG181" s="94"/>
+      <c r="AJ181" s="8"/>
       <c r="AM181" s="7"/>
-    </row>
-    <row r="182" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AO181" s="8"/>
+    </row>
+    <row r="182" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C182" s="7"/>
+      <c r="G182" s="8"/>
+      <c r="J182" s="73"/>
+      <c r="K182" s="73"/>
+      <c r="L182" s="73"/>
+      <c r="M182" s="73"/>
+      <c r="N182" s="73"/>
+      <c r="O182" s="73"/>
+      <c r="P182" s="73"/>
+      <c r="Q182" s="73"/>
+      <c r="R182" s="73"/>
+      <c r="S182" s="73"/>
+      <c r="T182" s="92"/>
+      <c r="U182" s="93"/>
+      <c r="V182" s="93"/>
+      <c r="W182" s="93"/>
+      <c r="X182" s="94"/>
+      <c r="Y182" s="92"/>
+      <c r="Z182" s="93"/>
+      <c r="AA182" s="93"/>
+      <c r="AB182" s="93"/>
+      <c r="AC182" s="93"/>
+      <c r="AD182" s="93"/>
+      <c r="AE182" s="93"/>
+      <c r="AF182" s="93"/>
+      <c r="AG182" s="94"/>
+      <c r="AJ182" s="8"/>
       <c r="AM182" s="7"/>
     </row>
-    <row r="183" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C183" s="7"/>
+      <c r="G183" s="8"/>
+      <c r="J183" s="73"/>
+      <c r="K183" s="73"/>
+      <c r="L183" s="73"/>
+      <c r="M183" s="73"/>
+      <c r="N183" s="73"/>
+      <c r="O183" s="73"/>
+      <c r="P183" s="73"/>
+      <c r="Q183" s="73"/>
+      <c r="R183" s="73"/>
+      <c r="S183" s="73"/>
+      <c r="T183" s="92"/>
+      <c r="U183" s="93"/>
+      <c r="V183" s="93"/>
+      <c r="W183" s="93"/>
+      <c r="X183" s="94"/>
+      <c r="Y183" s="92"/>
+      <c r="Z183" s="93"/>
+      <c r="AA183" s="93"/>
+      <c r="AB183" s="93"/>
+      <c r="AC183" s="93"/>
+      <c r="AD183" s="93"/>
+      <c r="AE183" s="93"/>
+      <c r="AF183" s="93"/>
+      <c r="AG183" s="94"/>
+      <c r="AJ183" s="8"/>
       <c r="AM183" s="7"/>
     </row>
-    <row r="184" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C184" s="7"/>
+      <c r="G184" s="8"/>
+      <c r="J184" s="73"/>
+      <c r="K184" s="73"/>
+      <c r="L184" s="73"/>
+      <c r="M184" s="73"/>
+      <c r="N184" s="73"/>
+      <c r="O184" s="73"/>
+      <c r="P184" s="73"/>
+      <c r="Q184" s="73"/>
+      <c r="R184" s="73"/>
+      <c r="S184" s="73"/>
+      <c r="T184" s="92"/>
+      <c r="U184" s="93"/>
+      <c r="V184" s="93"/>
+      <c r="W184" s="93"/>
+      <c r="X184" s="94"/>
+      <c r="Y184" s="92"/>
+      <c r="Z184" s="93"/>
+      <c r="AA184" s="93"/>
+      <c r="AB184" s="93"/>
+      <c r="AC184" s="93"/>
+      <c r="AD184" s="93"/>
+      <c r="AE184" s="93"/>
+      <c r="AF184" s="93"/>
+      <c r="AG184" s="94"/>
+      <c r="AJ184" s="8"/>
       <c r="AM184" s="7"/>
     </row>
-    <row r="185" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C185" s="7"/>
+      <c r="G185" s="8"/>
+      <c r="J185" s="73"/>
+      <c r="K185" s="73"/>
+      <c r="L185" s="73"/>
+      <c r="M185" s="73"/>
+      <c r="N185" s="73"/>
+      <c r="O185" s="73"/>
+      <c r="P185" s="73"/>
+      <c r="Q185" s="73"/>
+      <c r="R185" s="73"/>
+      <c r="S185" s="73"/>
+      <c r="T185" s="92"/>
+      <c r="U185" s="93"/>
+      <c r="V185" s="93"/>
+      <c r="W185" s="93"/>
+      <c r="X185" s="94"/>
+      <c r="Y185" s="92"/>
+      <c r="Z185" s="93"/>
+      <c r="AA185" s="93"/>
+      <c r="AB185" s="93"/>
+      <c r="AC185" s="93"/>
+      <c r="AD185" s="93"/>
+      <c r="AE185" s="93"/>
+      <c r="AF185" s="93"/>
+      <c r="AG185" s="94"/>
+      <c r="AJ185" s="8"/>
       <c r="AM185" s="7"/>
     </row>
-    <row r="186" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C186" s="7"/>
+      <c r="G186" s="8"/>
+      <c r="J186" s="73"/>
+      <c r="K186" s="73"/>
+      <c r="L186" s="73"/>
+      <c r="M186" s="73"/>
+      <c r="N186" s="73"/>
+      <c r="O186" s="73"/>
+      <c r="P186" s="73"/>
+      <c r="Q186" s="73"/>
+      <c r="R186" s="73"/>
+      <c r="S186" s="73"/>
+      <c r="T186" s="92"/>
+      <c r="U186" s="93"/>
+      <c r="V186" s="93"/>
+      <c r="W186" s="93"/>
+      <c r="X186" s="94"/>
+      <c r="Y186" s="92"/>
+      <c r="Z186" s="93"/>
+      <c r="AA186" s="93"/>
+      <c r="AB186" s="93"/>
+      <c r="AC186" s="93"/>
+      <c r="AD186" s="93"/>
+      <c r="AE186" s="93"/>
+      <c r="AF186" s="93"/>
+      <c r="AG186" s="94"/>
+      <c r="AJ186" s="8"/>
       <c r="AM186" s="7"/>
     </row>
-    <row r="187" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C187" s="7"/>
+      <c r="G187" s="8"/>
+      <c r="J187" s="73"/>
+      <c r="K187" s="73"/>
+      <c r="L187" s="73"/>
+      <c r="M187" s="73"/>
+      <c r="N187" s="73"/>
+      <c r="O187" s="73"/>
+      <c r="P187" s="73"/>
+      <c r="Q187" s="73"/>
+      <c r="R187" s="73"/>
+      <c r="S187" s="73"/>
+      <c r="T187" s="92"/>
+      <c r="U187" s="93"/>
+      <c r="V187" s="93"/>
+      <c r="W187" s="93"/>
+      <c r="X187" s="94"/>
+      <c r="Y187" s="92"/>
+      <c r="Z187" s="93"/>
+      <c r="AA187" s="93"/>
+      <c r="AB187" s="93"/>
+      <c r="AC187" s="93"/>
+      <c r="AD187" s="93"/>
+      <c r="AE187" s="93"/>
+      <c r="AF187" s="93"/>
+      <c r="AG187" s="94"/>
+      <c r="AJ187" s="8"/>
       <c r="AM187" s="7"/>
     </row>
-    <row r="188" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C188" s="7"/>
+      <c r="G188" s="8"/>
+      <c r="J188" s="73"/>
+      <c r="K188" s="73"/>
+      <c r="L188" s="73"/>
+      <c r="M188" s="73"/>
+      <c r="N188" s="73"/>
+      <c r="O188" s="73"/>
+      <c r="P188" s="73"/>
+      <c r="Q188" s="73"/>
+      <c r="R188" s="73"/>
+      <c r="S188" s="73"/>
+      <c r="T188" s="92"/>
+      <c r="U188" s="93"/>
+      <c r="V188" s="93"/>
+      <c r="W188" s="93"/>
+      <c r="X188" s="94"/>
+      <c r="Y188" s="92"/>
+      <c r="Z188" s="93"/>
+      <c r="AA188" s="93"/>
+      <c r="AB188" s="93"/>
+      <c r="AC188" s="93"/>
+      <c r="AD188" s="93"/>
+      <c r="AE188" s="93"/>
+      <c r="AF188" s="93"/>
+      <c r="AG188" s="94"/>
+      <c r="AJ188" s="8"/>
       <c r="AM188" s="7"/>
     </row>
-    <row r="189" spans="39:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C189" s="7"/>
+      <c r="G189" s="8"/>
+      <c r="J189" s="73"/>
+      <c r="K189" s="73"/>
+      <c r="L189" s="73"/>
+      <c r="M189" s="73"/>
+      <c r="N189" s="73"/>
+      <c r="O189" s="73"/>
+      <c r="P189" s="73"/>
+      <c r="Q189" s="73"/>
+      <c r="R189" s="73"/>
+      <c r="S189" s="73"/>
+      <c r="T189" s="92"/>
+      <c r="U189" s="93"/>
+      <c r="V189" s="93"/>
+      <c r="W189" s="93"/>
+      <c r="X189" s="94"/>
+      <c r="Y189" s="92"/>
+      <c r="Z189" s="93"/>
+      <c r="AA189" s="93"/>
+      <c r="AB189" s="93"/>
+      <c r="AC189" s="93"/>
+      <c r="AD189" s="93"/>
+      <c r="AE189" s="93"/>
+      <c r="AF189" s="93"/>
+      <c r="AG189" s="94"/>
+      <c r="AJ189" s="8"/>
       <c r="AM189" s="7"/>
     </row>
+    <row r="190" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C190" s="7"/>
+      <c r="G190" s="8"/>
+      <c r="J190" s="73"/>
+      <c r="K190" s="73"/>
+      <c r="L190" s="73"/>
+      <c r="M190" s="73"/>
+      <c r="N190" s="73"/>
+      <c r="O190" s="73"/>
+      <c r="P190" s="73"/>
+      <c r="Q190" s="73"/>
+      <c r="R190" s="73"/>
+      <c r="S190" s="73"/>
+      <c r="T190" s="92"/>
+      <c r="U190" s="93"/>
+      <c r="V190" s="93"/>
+      <c r="W190" s="93"/>
+      <c r="X190" s="94"/>
+      <c r="Y190" s="92"/>
+      <c r="Z190" s="93"/>
+      <c r="AA190" s="93"/>
+      <c r="AB190" s="93"/>
+      <c r="AC190" s="93"/>
+      <c r="AD190" s="93"/>
+      <c r="AE190" s="93"/>
+      <c r="AF190" s="93"/>
+      <c r="AG190" s="94"/>
+      <c r="AJ190" s="8"/>
+      <c r="AM190" s="7"/>
+    </row>
+    <row r="191" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C191" s="7"/>
+      <c r="G191" s="8"/>
+      <c r="J191" s="73"/>
+      <c r="K191" s="73"/>
+      <c r="L191" s="73"/>
+      <c r="M191" s="73"/>
+      <c r="N191" s="73"/>
+      <c r="O191" s="73"/>
+      <c r="P191" s="73"/>
+      <c r="Q191" s="73"/>
+      <c r="R191" s="73"/>
+      <c r="S191" s="73"/>
+      <c r="T191" s="92"/>
+      <c r="U191" s="93"/>
+      <c r="V191" s="93"/>
+      <c r="W191" s="93"/>
+      <c r="X191" s="94"/>
+      <c r="Y191" s="92"/>
+      <c r="Z191" s="93"/>
+      <c r="AA191" s="93"/>
+      <c r="AB191" s="93"/>
+      <c r="AC191" s="93"/>
+      <c r="AD191" s="93"/>
+      <c r="AE191" s="93"/>
+      <c r="AF191" s="93"/>
+      <c r="AG191" s="94"/>
+      <c r="AJ191" s="8"/>
+    </row>
+    <row r="192" spans="3:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C192" s="7"/>
+      <c r="G192" s="8"/>
+      <c r="J192" s="73"/>
+      <c r="K192" s="73"/>
+      <c r="L192" s="73"/>
+      <c r="M192" s="73"/>
+      <c r="N192" s="73"/>
+      <c r="O192" s="73"/>
+      <c r="P192" s="73"/>
+      <c r="Q192" s="73"/>
+      <c r="R192" s="73"/>
+      <c r="S192" s="73"/>
+      <c r="T192" s="92"/>
+      <c r="U192" s="93"/>
+      <c r="V192" s="93"/>
+      <c r="W192" s="93"/>
+      <c r="X192" s="94"/>
+      <c r="Y192" s="92"/>
+      <c r="Z192" s="93"/>
+      <c r="AA192" s="93"/>
+      <c r="AB192" s="93"/>
+      <c r="AC192" s="93"/>
+      <c r="AD192" s="93"/>
+      <c r="AE192" s="93"/>
+      <c r="AF192" s="93"/>
+      <c r="AG192" s="94"/>
+      <c r="AJ192" s="8"/>
+    </row>
+    <row r="193" spans="3:36" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C193" s="7"/>
+      <c r="G193" s="8"/>
+      <c r="AJ193" s="8"/>
+    </row>
+    <row r="194" spans="3:36" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C194" s="9"/>
+      <c r="D194" s="10"/>
+      <c r="E194" s="10"/>
+      <c r="F194" s="10"/>
+      <c r="G194" s="11"/>
+      <c r="H194" s="10"/>
+      <c r="I194" s="10"/>
+      <c r="J194" s="10"/>
+      <c r="K194" s="10"/>
+      <c r="L194" s="10"/>
+      <c r="M194" s="10"/>
+      <c r="N194" s="10"/>
+      <c r="O194" s="10"/>
+      <c r="P194" s="10"/>
+      <c r="Q194" s="10"/>
+      <c r="R194" s="10"/>
+      <c r="S194" s="10"/>
+      <c r="T194" s="10"/>
+      <c r="U194" s="10"/>
+      <c r="V194" s="10"/>
+      <c r="W194" s="10"/>
+      <c r="X194" s="10"/>
+      <c r="Y194" s="10"/>
+      <c r="Z194" s="10"/>
+      <c r="AA194" s="10"/>
+      <c r="AB194" s="10"/>
+      <c r="AC194" s="10"/>
+      <c r="AD194" s="10"/>
+      <c r="AE194" s="10"/>
+      <c r="AF194" s="10"/>
+      <c r="AG194" s="10"/>
+      <c r="AH194" s="10"/>
+      <c r="AI194" s="10"/>
+      <c r="AJ194" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="539">
+  <mergeCells count="625">
+    <mergeCell ref="J192:M192"/>
+    <mergeCell ref="N192:Q192"/>
+    <mergeCell ref="R192:S192"/>
+    <mergeCell ref="T192:X192"/>
+    <mergeCell ref="Y192:AG192"/>
+    <mergeCell ref="J190:M190"/>
+    <mergeCell ref="N190:Q190"/>
+    <mergeCell ref="R190:S190"/>
+    <mergeCell ref="T190:X190"/>
+    <mergeCell ref="Y190:AG190"/>
+    <mergeCell ref="J191:M191"/>
+    <mergeCell ref="N191:Q191"/>
+    <mergeCell ref="R191:S191"/>
+    <mergeCell ref="T191:X191"/>
+    <mergeCell ref="Y191:AG191"/>
+    <mergeCell ref="J188:M188"/>
+    <mergeCell ref="N188:Q188"/>
+    <mergeCell ref="R188:S188"/>
+    <mergeCell ref="T188:X188"/>
+    <mergeCell ref="Y188:AG188"/>
+    <mergeCell ref="J189:M189"/>
+    <mergeCell ref="N189:Q189"/>
+    <mergeCell ref="R189:S189"/>
+    <mergeCell ref="T189:X189"/>
+    <mergeCell ref="Y189:AG189"/>
+    <mergeCell ref="J186:M186"/>
+    <mergeCell ref="N186:Q186"/>
+    <mergeCell ref="R186:S186"/>
+    <mergeCell ref="T186:X186"/>
+    <mergeCell ref="Y186:AG186"/>
+    <mergeCell ref="J187:M187"/>
+    <mergeCell ref="N187:Q187"/>
+    <mergeCell ref="R187:S187"/>
+    <mergeCell ref="T187:X187"/>
+    <mergeCell ref="Y187:AG187"/>
+    <mergeCell ref="J184:M184"/>
+    <mergeCell ref="N184:Q184"/>
+    <mergeCell ref="R184:S184"/>
+    <mergeCell ref="T184:X184"/>
+    <mergeCell ref="Y184:AG184"/>
+    <mergeCell ref="J185:M185"/>
+    <mergeCell ref="N185:Q185"/>
+    <mergeCell ref="R185:S185"/>
+    <mergeCell ref="T185:X185"/>
+    <mergeCell ref="Y185:AG185"/>
+    <mergeCell ref="J182:M182"/>
+    <mergeCell ref="N182:Q182"/>
+    <mergeCell ref="R182:S182"/>
+    <mergeCell ref="T182:X182"/>
+    <mergeCell ref="Y182:AG182"/>
+    <mergeCell ref="J183:M183"/>
+    <mergeCell ref="N183:Q183"/>
+    <mergeCell ref="R183:S183"/>
+    <mergeCell ref="T183:X183"/>
+    <mergeCell ref="Y183:AG183"/>
+    <mergeCell ref="J180:M180"/>
+    <mergeCell ref="N180:Q180"/>
+    <mergeCell ref="R180:S180"/>
+    <mergeCell ref="T180:X180"/>
+    <mergeCell ref="Y180:AG180"/>
+    <mergeCell ref="J181:M181"/>
+    <mergeCell ref="N181:Q181"/>
+    <mergeCell ref="R181:S181"/>
+    <mergeCell ref="T181:X181"/>
+    <mergeCell ref="Y181:AG181"/>
+    <mergeCell ref="J178:M178"/>
+    <mergeCell ref="N178:Q178"/>
+    <mergeCell ref="R178:S178"/>
+    <mergeCell ref="T178:X178"/>
+    <mergeCell ref="Y178:AG178"/>
+    <mergeCell ref="J179:M179"/>
+    <mergeCell ref="N179:Q179"/>
+    <mergeCell ref="R179:S179"/>
+    <mergeCell ref="T179:X179"/>
+    <mergeCell ref="Y179:AG179"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="N175:Q175"/>
+    <mergeCell ref="T175:W175"/>
+    <mergeCell ref="Z175:AA175"/>
+    <mergeCell ref="AB175:AC175"/>
+    <mergeCell ref="AF175:AG175"/>
+    <mergeCell ref="J177:M177"/>
+    <mergeCell ref="N177:Q177"/>
+    <mergeCell ref="R177:S177"/>
+    <mergeCell ref="T177:X177"/>
+    <mergeCell ref="Y177:AG177"/>
     <mergeCell ref="J164:M164"/>
     <mergeCell ref="N164:Q164"/>
     <mergeCell ref="R164:S164"/>
@@ -22594,8 +23822,6 @@
     <mergeCell ref="AL3:AO4"/>
     <mergeCell ref="O4:S4"/>
     <mergeCell ref="AI1:AK2"/>
-    <mergeCell ref="A6:AO6"/>
-    <mergeCell ref="D83:AM118"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
@@ -22605,6 +23831,8 @@
     <mergeCell ref="D123:AN133"/>
     <mergeCell ref="D78:AN79"/>
     <mergeCell ref="D35:AM39"/>
+    <mergeCell ref="A6:AO6"/>
+    <mergeCell ref="D83:AM118"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
